--- a/src/main/resources/doc/PONKIDS-테이블정의서_v3.0.xlsx
+++ b/src/main/resources/doc/PONKIDS-테이블정의서_v3.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jjeoV/Desktop/jjeoV/2023/pioneerKids/workspace/ponkidsDev/ponkids/src/main/resources/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDDB978-F83C-2B45-82BA-111A17192297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8D86CD-0B01-2748-A148-48E0E076934C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="860" windowWidth="34200" windowHeight="21380" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="880" windowWidth="34200" windowHeight="21380" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="테이블정의서" sheetId="26" r:id="rId1"/>
@@ -27,16 +27,16 @@
     <definedName name="ㄴ">#REF!</definedName>
     <definedName name="버전" localSheetId="0">#REF!</definedName>
     <definedName name="버전">#REF!</definedName>
-    <definedName name="사업명">[2]표지!$B$43</definedName>
-    <definedName name="baseline" localSheetId="0">'[1]2.일정추적'!#REF!</definedName>
-    <definedName name="baseline">'[1]2.일정추적'!#REF!</definedName>
+    <definedName name="사업명">[1]표지!$B$43</definedName>
+    <definedName name="baseline" localSheetId="0">'[2]2.일정추적'!#REF!</definedName>
+    <definedName name="baseline">'[2]2.일정추적'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'테이블 목록'!$A$1:$F$18</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">테이블정의서!$B$1:$S$42</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'테이블 목록'!$1:$3</definedName>
-    <definedName name="rpt_date">'[1]1.요약'!$C$4</definedName>
+    <definedName name="rpt_date">'[2]1.요약'!$C$4</definedName>
     <definedName name="T01_컬럼정보_Query" localSheetId="0">#REF!</definedName>
     <definedName name="T01_컬럼정보_Query">#REF!</definedName>
-    <definedName name="tol">'[1]4.1공수분석_개발'!$J$6</definedName>
+    <definedName name="tol">'[2]4.1공수분석_개발'!$J$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4310" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4312" uniqueCount="775">
   <si>
     <t>테이블명</t>
     <phoneticPr fontId="12" type="noConversion"/>
@@ -3101,6 +3101,22 @@
   </si>
   <si>
     <t>NEW_WINDOW_YN</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>CN_ATCH_FILE_SN</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용첨부파일일련번호</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>썸네일용</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용에 들어갈 첨부파일</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -4438,23 +4454,6 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="2.일정추적"/>
-      <sheetName val="1.요약"/>
-      <sheetName val="4.1공수분석_개발"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
       <sheetName val="표지"/>
       <sheetName val="제개정이력"/>
       <sheetName val="업무분류코드"/>
@@ -4483,6 +4482,23 @@
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="2.일정추적"/>
+      <sheetName val="1.요약"/>
+      <sheetName val="4.1공수분석_개발"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -24532,10 +24548,10 @@
         <v>5</v>
       </c>
       <c r="G220" s="106" t="s">
-        <v>380</v>
+        <v>521</v>
       </c>
       <c r="H220" s="106" t="s">
-        <v>382</v>
+        <v>520</v>
       </c>
       <c r="I220" s="69"/>
       <c r="J220" s="61"/>
@@ -24564,7 +24580,9 @@
       </c>
       <c r="T220" s="132"/>
       <c r="U220" s="130"/>
-      <c r="V220" s="109"/>
+      <c r="V220" s="109" t="s">
+        <v>773</v>
+      </c>
       <c r="W220" s="90"/>
       <c r="X220" s="130"/>
       <c r="Y220" s="129" t="str">
@@ -24573,11 +24591,11 @@
       </c>
       <c r="Z220" s="50" t="str">
         <f t="shared" si="64"/>
-        <v>THUMB_ATCH_FILE_SN INTEGER,</v>
+        <v>ATCH_FILE_SN INTEGER,</v>
       </c>
       <c r="AA220" s="50" t="str">
         <f t="shared" si="61"/>
-        <v>ALTER TABLE TB_NTT ADD CONSTRAINT TB_NTT_FKEY2 FOREIGN KEY(THUMB_ATCH_FILE_SN) REFERENCES TB_ATCH_FILE(ATCH_FILE_SN) ON UPDATE CASCADE ON DELETE SET NULL;</v>
+        <v>ALTER TABLE TB_NTT ADD CONSTRAINT TB_NTT_FKEY2 FOREIGN KEY(ATCH_FILE_SN) REFERENCES TB_ATCH_FILE(ATCH_FILE_SN) ON UPDATE CASCADE ON DELETE SET NULL;</v>
       </c>
       <c r="AB220" s="50" t="str">
         <f t="shared" si="62"/>
@@ -24589,15 +24607,15 @@
       </c>
       <c r="AD220" s="50" t="str">
         <f t="shared" si="56"/>
-        <v>ALTER TABLE TB_NTT ALTER COLUMN THUMB_ATCH_FILE_SN TYPE INTEGER;</v>
+        <v>ALTER TABLE TB_NTT ALTER COLUMN ATCH_FILE_SN TYPE INTEGER;</v>
       </c>
       <c r="AE220" s="50" t="str">
         <f t="shared" si="57"/>
-        <v>ALTER TABLE TB_NTT ADD COLUMN THUMB_ATCH_FILE_SN INTEGER;</v>
+        <v>ALTER TABLE TB_NTT ADD COLUMN ATCH_FILE_SN INTEGER;</v>
       </c>
       <c r="AF220" s="50" t="str">
         <f t="shared" si="58"/>
-        <v>ALTER TABLE TB_NTT DROP COLUMN THUMB_ATCH_FILE_SN;</v>
+        <v>ALTER TABLE TB_NTT DROP COLUMN ATCH_FILE_SN;</v>
       </c>
       <c r="AG220" s="50" t="str">
         <f t="shared" si="59"/>
@@ -24605,7 +24623,7 @@
       </c>
       <c r="AH220" s="50" t="str">
         <f t="shared" si="63"/>
-        <v>COMMENT ON COLUMN TB_NTT.THUMB_ATCH_FILE_SN IS '썸네일 첨부 파일 일련번호' ;</v>
+        <v>COMMENT ON COLUMN TB_NTT.ATCH_FILE_SN IS '썸네일 첨부 파일 일련번호' ;</v>
       </c>
     </row>
     <row r="221" spans="1:34" ht="20" customHeight="1">
@@ -24714,10 +24732,10 @@
         <v>7</v>
       </c>
       <c r="G222" s="105" t="s">
-        <v>379</v>
+        <v>771</v>
       </c>
       <c r="H222" s="105" t="s">
-        <v>381</v>
+        <v>772</v>
       </c>
       <c r="I222" s="45"/>
       <c r="J222" s="45"/>
@@ -24746,7 +24764,9 @@
       </c>
       <c r="T222" s="83"/>
       <c r="U222" s="83"/>
-      <c r="V222" s="106"/>
+      <c r="V222" s="106" t="s">
+        <v>774</v>
+      </c>
       <c r="W222" s="45"/>
       <c r="X222" s="83"/>
       <c r="Y222" s="129" t="str">
@@ -24755,11 +24775,11 @@
       </c>
       <c r="Z222" s="50" t="str">
         <f t="shared" si="64"/>
-        <v>ATCH_FILE_SN INTEGER,</v>
+        <v>CN_ATCH_FILE_SN INTEGER,</v>
       </c>
       <c r="AA222" s="50" t="str">
         <f t="shared" si="61"/>
-        <v>ALTER TABLE TB_NTT ADD CONSTRAINT TB_NTT_FKEY3 FOREIGN KEY(ATCH_FILE_SN) REFERENCES TB_ATCH_FILE(ATCH_FILE_SN) ON UPDATE CASCADE ON DELETE SET NULL;</v>
+        <v>ALTER TABLE TB_NTT ADD CONSTRAINT TB_NTT_FKEY3 FOREIGN KEY(CN_ATCH_FILE_SN) REFERENCES TB_ATCH_FILE(ATCH_FILE_SN) ON UPDATE CASCADE ON DELETE SET NULL;</v>
       </c>
       <c r="AB222" s="50" t="str">
         <f t="shared" si="62"/>
@@ -24771,15 +24791,15 @@
       </c>
       <c r="AD222" s="50" t="str">
         <f t="shared" si="56"/>
-        <v>ALTER TABLE TB_NTT ALTER COLUMN ATCH_FILE_SN TYPE INTEGER;</v>
+        <v>ALTER TABLE TB_NTT ALTER COLUMN CN_ATCH_FILE_SN TYPE INTEGER;</v>
       </c>
       <c r="AE222" s="50" t="str">
         <f t="shared" si="57"/>
-        <v>ALTER TABLE TB_NTT ADD COLUMN ATCH_FILE_SN INTEGER;</v>
+        <v>ALTER TABLE TB_NTT ADD COLUMN CN_ATCH_FILE_SN INTEGER;</v>
       </c>
       <c r="AF222" s="50" t="str">
         <f t="shared" si="58"/>
-        <v>ALTER TABLE TB_NTT DROP COLUMN ATCH_FILE_SN;</v>
+        <v>ALTER TABLE TB_NTT DROP COLUMN CN_ATCH_FILE_SN;</v>
       </c>
       <c r="AG222" s="50" t="str">
         <f t="shared" si="59"/>
@@ -24787,7 +24807,7 @@
       </c>
       <c r="AH222" s="50" t="str">
         <f t="shared" si="63"/>
-        <v>COMMENT ON COLUMN TB_NTT.ATCH_FILE_SN IS '첨부 파일 일련번호' ;</v>
+        <v>COMMENT ON COLUMN TB_NTT.CN_ATCH_FILE_SN IS '첨부 파일 일련번호' ;</v>
       </c>
     </row>
     <row r="223" spans="1:34" ht="20" customHeight="1">
